--- a/01-Requirements/04-User_Stories.xlsx
+++ b/01-Requirements/04-User_Stories.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my things\SQA projects\QADemo E-Commerce Application Manual Testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my things\SQA projects\QADemo E-Commerce Application Manual Testing\QADemoE-CommerceApplicationManualTesting\01-Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A506E0F-9AAE-4270-B84C-0755D43ADC95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80875917-A661-419A-9320-9555A9896DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,9 +33,6 @@
     <t>Value</t>
   </si>
   <si>
-    <t>Requirement Analysis Document</t>
-  </si>
-  <si>
     <t>QADemo E-Commerce Application</t>
   </si>
   <si>
@@ -434,6 +431,9 @@
     <t>As a customer, 
 I want to view the description of a product, 
 so that I can make an informed purchasing decision.</t>
+  </si>
+  <si>
+    <t>User Stories</t>
   </si>
 </sst>
 </file>
@@ -963,593 +963,593 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2</v>
+        <v>118</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="12" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D12" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>35</v>
-      </c>
       <c r="E15" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="E16" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="E17" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="E18" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="E19" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="C20" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="E21" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="E23" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>55</v>
-      </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="E25" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="E26" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>61</v>
-      </c>
       <c r="C27" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D27" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>116</v>
-      </c>
       <c r="F27" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>63</v>
-      </c>
       <c r="E28" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>66</v>
-      </c>
       <c r="E29" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="E32" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="E33" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>86</v>
-      </c>
       <c r="E34" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="E38" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
